--- a/TestData/LV_TMTC0034038_VerifyTheFunctionalityOfTheFinancialSponsorsTabOnCompanyDetailPage.xlsx
+++ b/TestData/LV_TMTC0034038_VerifyTheFunctionalityOfTheFinancialSponsorsTabOnCompanyDetailPage.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3346AE8-E15D-42BE-81EA-1967528C2DCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BFB8458-22D8-4840-BB5C-2995A8E0EBC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="984" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="708" windowWidth="23256" windowHeight="12456" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="Buttons" sheetId="6" r:id="rId5"/>
     <sheet name="TabName" sheetId="14" r:id="rId6"/>
     <sheet name="Investment" sheetId="15" r:id="rId7"/>
+    <sheet name="section" sheetId="16" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="67">
   <si>
     <t>CompanyType</t>
   </si>
@@ -225,6 +226,24 @@
   </si>
   <si>
     <t>Portfolio Companies</t>
+  </si>
+  <si>
+    <t>Current Sponsors</t>
+  </si>
+  <si>
+    <t>Previous Sponsors</t>
+  </si>
+  <si>
+    <t>Current Investments</t>
+  </si>
+  <si>
+    <t>Prior Investments</t>
+  </si>
+  <si>
+    <t>OCSection</t>
+  </si>
+  <si>
+    <t>CPSection</t>
   </si>
 </sst>
 </file>
@@ -256,7 +275,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -264,15 +283,41 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -555,13 +600,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>27</v>
       </c>
@@ -569,7 +614,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>40</v>
       </c>
@@ -577,7 +622,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -594,14 +639,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBDC019B-D24C-4D11-B55C-3110A9446A1A}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>29</v>
       </c>
@@ -614,22 +659,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF90D989-9E82-487D-8276-51E2EA9B068E}">
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>45</v>
       </c>
@@ -642,28 +687,28 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="18" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.42578125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="22" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="21.88671875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="21.109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -719,7 +764,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -775,7 +820,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -797,19 +842,19 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F8B8E47-1D86-45C9-83BF-075D8B336916}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>33</v>
       </c>
@@ -822,13 +867,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C0757D6-F763-43B8-B4D7-D75C2D24FC4C}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>52</v>
       </c>
@@ -836,7 +881,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>51</v>
       </c>
@@ -844,7 +889,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>60</v>
       </c>
@@ -860,32 +905,33 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8437F5F6-DA3C-47BD-BE9B-603C724AB359}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="6" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="6" t="s">
         <v>59</v>
       </c>
     </row>
@@ -893,4 +939,42 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04EB679A-1DFE-46E5-BE1B-3B27BC6F42FE}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>